--- a/test_data_random.xlsx
+++ b/test_data_random.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17150" windowHeight="10890"/>
+    <workbookView windowWidth="25600" windowHeight="11720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1088,7 +1088,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4">
-        <v>46086.4180555556</v>
+        <v>46086.41875</v>
       </c>
       <c r="B5" s="2">
         <v>85</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4">
-        <v>46086.41875</v>
+        <v>46086.4194444444</v>
       </c>
       <c r="B6" s="2">
         <v>90</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="4">
-        <v>46086.4194444444</v>
+        <v>46086.4201388889</v>
       </c>
       <c r="B7" s="2">
         <v>82</v>
@@ -1139,7 +1139,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="4">
-        <v>46086.4201388889</v>
+        <v>46086.4208333333</v>
       </c>
       <c r="B8" s="2">
         <v>106</v>
@@ -1156,7 +1156,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="4">
-        <v>46086.4208333333</v>
+        <v>46086.4215277778</v>
       </c>
       <c r="B9" s="2">
         <v>80</v>
@@ -1173,7 +1173,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="4">
-        <v>46086.4215277778</v>
+        <v>46086.4222222222</v>
       </c>
       <c r="B10" s="2">
         <v>74</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="4">
-        <v>46086.4222222222</v>
+        <v>46086.4229166667</v>
       </c>
       <c r="B11" s="2">
         <v>118</v>
@@ -1207,7 +1207,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4">
-        <v>46086.4229166667</v>
+        <v>46086.4236111111</v>
       </c>
       <c r="B12" s="2">
         <v>88</v>
@@ -1224,7 +1224,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="4">
-        <v>46086.4236111111</v>
+        <v>46086.4243055556</v>
       </c>
       <c r="B13" s="2">
         <v>78</v>
@@ -1241,7 +1241,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="4">
-        <v>46086.4243055556</v>
+        <v>46086.425</v>
       </c>
       <c r="B14" s="2">
         <v>74</v>
